--- a/r5-core-40-dead-code-removal/StructureDefinition-at-core-valueset.xlsx
+++ b/r5-core-40-dead-code-removal/StructureDefinition-at-core-valueset.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-17T19:30:30+00:00</t>
+    <t>2024-11-22T07:57:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
